--- a/Result/profitability/3675.xlsx
+++ b/Result/profitability/3675.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM69"/>
+  <dimension ref="A1:AM70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.42</v>
       </c>
       <c r="M2" t="n">
-        <v>1.07625</v>
+        <v>1.06375</v>
       </c>
       <c r="N2" t="n">
-        <v>33.99625</v>
+        <v>33.855</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.84</v>
       </c>
       <c r="M3" t="n">
-        <v>0.9187500000000001</v>
+        <v>0.9287500000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>30.45875</v>
+        <v>30.58125</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.7</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8912499999999999</v>
+        <v>0.9724999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>27.48125</v>
+        <v>27.8375</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -911,7 +911,7 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.28</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8825</v>
+        <v>1.24375</v>
       </c>
       <c r="N5" t="n">
-        <v>24.68625</v>
+        <v>25.71125</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>99.09999999999999</v>
@@ -1137,10 +1137,10 @@
         <v>0.87</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1025</v>
+        <v>1.22</v>
       </c>
       <c r="N6" t="n">
-        <v>22.555</v>
+        <v>23.66875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.78</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0675</v>
+        <v>1.175</v>
       </c>
       <c r="N7" t="n">
-        <v>20.17375</v>
+        <v>20.71125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.12</v>
       </c>
       <c r="M8" t="n">
-        <v>0.91</v>
+        <v>0.9712499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>17.70125</v>
+        <v>18.02</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9191,6 +9191,133 @@
       </c>
       <c r="AM69" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>3675</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>801</v>
+      </c>
+      <c r="D70" t="n">
+        <v>474</v>
+      </c>
+      <c r="E70" t="n">
+        <v>327</v>
+      </c>
+      <c r="F70" t="n">
+        <v>40.81</v>
+      </c>
+      <c r="G70" t="n">
+        <v>141</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>17.63%</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" t="n">
+        <v>141</v>
+      </c>
+      <c r="K70" t="n">
+        <v>106</v>
+      </c>
+      <c r="L70" t="n">
+        <v>2</v>
+      </c>
+      <c r="M70" t="n">
+        <v>1.27375</v>
+      </c>
+      <c r="N70" t="n">
+        <v>37.4775</v>
+      </c>
+      <c r="O70" t="n">
+        <v>1</v>
+      </c>
+      <c r="P70" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+      <c r="S70" t="n">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>0</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
+      </c>
+      <c r="V70" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W70" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="X70" t="n">
+        <v>0.3245033112582782</v>
+      </c>
+      <c r="Y70" t="n">
+        <v>2.550000000000004</v>
+      </c>
+      <c r="Z70" t="n">
+        <v>0.06664924202822808</v>
+      </c>
+      <c r="AA70" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AB70" t="n">
+        <v>-3.247191011235955</v>
+      </c>
+      <c r="AC70" t="n">
+        <v>8.200000000000003</v>
+      </c>
+      <c r="AD70" t="n">
+        <v>0.2514566084023306</v>
+      </c>
+      <c r="AE70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI70" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ70" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK70" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL70" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM70" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
